--- a/fil-c-x64/Scattered successful looukp.xlsx
+++ b/fil-c-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>12.2246</v>
+        <v>12.4374</v>
       </c>
       <c r="C2" t="n">
-        <v>17.0513</v>
+        <v>17.4187</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2051</v>
+        <v>25.2951</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1639</v>
+        <v>14.2771</v>
       </c>
       <c r="F2" t="n">
-        <v>17.009</v>
+        <v>16.7791</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>12.6524</v>
+        <v>12.5097</v>
       </c>
       <c r="C3" t="n">
-        <v>17.669</v>
+        <v>16.9137</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7718</v>
+        <v>25.9036</v>
       </c>
       <c r="E3" t="n">
-        <v>14.3515</v>
+        <v>14.268</v>
       </c>
       <c r="F3" t="n">
-        <v>17.7165</v>
+        <v>17.0061</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>12.546</v>
+        <v>12.637</v>
       </c>
       <c r="C4" t="n">
-        <v>17.8017</v>
+        <v>17.6313</v>
       </c>
       <c r="D4" t="n">
-        <v>26.2806</v>
+        <v>26.4519</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5548</v>
+        <v>14.5279</v>
       </c>
       <c r="F4" t="n">
-        <v>17.0913</v>
+        <v>17.5782</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>12.9739</v>
+        <v>13.1201</v>
       </c>
       <c r="C5" t="n">
-        <v>17.6029</v>
+        <v>17.7409</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8461</v>
+        <v>27.139</v>
       </c>
       <c r="E5" t="n">
-        <v>14.635</v>
+        <v>14.6679</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5858</v>
+        <v>17.4307</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>12.817</v>
+        <v>13.0657</v>
       </c>
       <c r="C6" t="n">
-        <v>18.3159</v>
+        <v>17.7601</v>
       </c>
       <c r="D6" t="n">
-        <v>27.4259</v>
+        <v>27.4256</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8374</v>
+        <v>14.7745</v>
       </c>
       <c r="F6" t="n">
-        <v>17.5974</v>
+        <v>17.8004</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.004</v>
+        <v>13.1795</v>
       </c>
       <c r="C7" t="n">
-        <v>18.0892</v>
+        <v>18.0483</v>
       </c>
       <c r="D7" t="n">
-        <v>24.1448</v>
+        <v>23.9157</v>
       </c>
       <c r="E7" t="n">
-        <v>15.5398</v>
+        <v>15.1951</v>
       </c>
       <c r="F7" t="n">
-        <v>18.0434</v>
+        <v>18.1193</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>13.2856</v>
+        <v>13.3696</v>
       </c>
       <c r="C8" t="n">
-        <v>17.9883</v>
+        <v>18.0609</v>
       </c>
       <c r="D8" t="n">
-        <v>24.1262</v>
+        <v>24.1301</v>
       </c>
       <c r="E8" t="n">
-        <v>15.8234</v>
+        <v>16.6316</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9962</v>
+        <v>19.3979</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.1217</v>
+        <v>13.3047</v>
       </c>
       <c r="C9" t="n">
-        <v>18.2457</v>
+        <v>18.4765</v>
       </c>
       <c r="D9" t="n">
-        <v>24.2378</v>
+        <v>24.664</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3527</v>
+        <v>14.4596</v>
       </c>
       <c r="F9" t="n">
-        <v>18.4926</v>
+        <v>19.9018</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>14.388</v>
+        <v>14.786</v>
       </c>
       <c r="C10" t="n">
-        <v>19.6504</v>
+        <v>20.2193</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0814</v>
+        <v>25.0775</v>
       </c>
       <c r="E10" t="n">
-        <v>15.2096</v>
+        <v>15.3124</v>
       </c>
       <c r="F10" t="n">
-        <v>18.9696</v>
+        <v>18.9107</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>14.7034</v>
+        <v>14.8223</v>
       </c>
       <c r="C11" t="n">
-        <v>20.0842</v>
+        <v>19.8741</v>
       </c>
       <c r="D11" t="n">
-        <v>25.0515</v>
+        <v>25.3868</v>
       </c>
       <c r="E11" t="n">
-        <v>14.4604</v>
+        <v>14.4608</v>
       </c>
       <c r="F11" t="n">
-        <v>18.9604</v>
+        <v>19.1676</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>13.932</v>
+        <v>14.6862</v>
       </c>
       <c r="C12" t="n">
-        <v>19.4361</v>
+        <v>19.9182</v>
       </c>
       <c r="D12" t="n">
-        <v>25.9148</v>
+        <v>25.5213</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7342</v>
+        <v>15.3624</v>
       </c>
       <c r="F12" t="n">
-        <v>18.7495</v>
+        <v>18.5024</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>14.467</v>
+        <v>15.2163</v>
       </c>
       <c r="C13" t="n">
-        <v>19.3993</v>
+        <v>19.8069</v>
       </c>
       <c r="D13" t="n">
-        <v>25.977</v>
+        <v>26.3642</v>
       </c>
       <c r="E13" t="n">
-        <v>14.5564</v>
+        <v>14.6707</v>
       </c>
       <c r="F13" t="n">
-        <v>18.3647</v>
+        <v>18.8582</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>14.5984</v>
+        <v>14.5839</v>
       </c>
       <c r="C14" t="n">
-        <v>19.4829</v>
+        <v>19.79</v>
       </c>
       <c r="D14" t="n">
-        <v>26.527</v>
+        <v>26.5219</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7457</v>
+        <v>14.7789</v>
       </c>
       <c r="F14" t="n">
-        <v>19.134</v>
+        <v>19.7046</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>14.6598</v>
+        <v>14.6593</v>
       </c>
       <c r="C15" t="n">
-        <v>19.9591</v>
+        <v>19.5566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.3652</v>
+        <v>26.9517</v>
       </c>
       <c r="E15" t="n">
-        <v>14.8729</v>
+        <v>14.8799</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7509</v>
+        <v>19.0405</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>14.7052</v>
+        <v>14.7033</v>
       </c>
       <c r="C16" t="n">
-        <v>19.5729</v>
+        <v>19.5665</v>
       </c>
       <c r="D16" t="n">
-        <v>27.4572</v>
+        <v>27.4483</v>
       </c>
       <c r="E16" t="n">
-        <v>15.2148</v>
+        <v>15.0366</v>
       </c>
       <c r="F16" t="n">
-        <v>19.0951</v>
+        <v>19.763</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.8912</v>
+        <v>14.107</v>
       </c>
       <c r="C17" t="n">
-        <v>19.6166</v>
+        <v>20.1285</v>
       </c>
       <c r="D17" t="n">
-        <v>28.2825</v>
+        <v>28.4181</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2477</v>
+        <v>15.2792</v>
       </c>
       <c r="F17" t="n">
-        <v>19.5945</v>
+        <v>19.6372</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>15.1101</v>
+        <v>14.9082</v>
       </c>
       <c r="C18" t="n">
-        <v>20.2596</v>
+        <v>20.1026</v>
       </c>
       <c r="D18" t="n">
-        <v>28.9862</v>
+        <v>29.1207</v>
       </c>
       <c r="E18" t="n">
-        <v>15.4004</v>
+        <v>15.7923</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6821</v>
+        <v>19.6293</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>15.0716</v>
+        <v>15.1795</v>
       </c>
       <c r="C19" t="n">
-        <v>20.2129</v>
+        <v>20.2743</v>
       </c>
       <c r="D19" t="n">
-        <v>29.4335</v>
+        <v>29.5274</v>
       </c>
       <c r="E19" t="n">
-        <v>15.7521</v>
+        <v>15.6782</v>
       </c>
       <c r="F19" t="n">
-        <v>20.6507</v>
+        <v>19.955</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>15.1828</v>
+        <v>15.1964</v>
       </c>
       <c r="C20" t="n">
-        <v>20.2154</v>
+        <v>20.4634</v>
       </c>
       <c r="D20" t="n">
-        <v>29.889</v>
+        <v>30.0255</v>
       </c>
       <c r="E20" t="n">
-        <v>15.8705</v>
+        <v>16.0837</v>
       </c>
       <c r="F20" t="n">
-        <v>20.8845</v>
+        <v>20.4073</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>15.0805</v>
+        <v>15.3131</v>
       </c>
       <c r="C21" t="n">
-        <v>20.2925</v>
+        <v>20.2586</v>
       </c>
       <c r="D21" t="n">
-        <v>25.3273</v>
+        <v>25.8936</v>
       </c>
       <c r="E21" t="n">
-        <v>16.2117</v>
+        <v>16.5456</v>
       </c>
       <c r="F21" t="n">
-        <v>19.6959</v>
+        <v>20.312</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>15.3204</v>
+        <v>15.3768</v>
       </c>
       <c r="C22" t="n">
-        <v>20.635</v>
+        <v>20.8877</v>
       </c>
       <c r="D22" t="n">
-        <v>26.0802</v>
+        <v>26.0413</v>
       </c>
       <c r="E22" t="n">
-        <v>16.9212</v>
+        <v>16.9972</v>
       </c>
       <c r="F22" t="n">
-        <v>21.8607</v>
+        <v>21.111</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0697</v>
+        <v>15.7634</v>
       </c>
       <c r="C23" t="n">
-        <v>20.8746</v>
+        <v>20.4002</v>
       </c>
       <c r="D23" t="n">
-        <v>26.2242</v>
+        <v>26.1481</v>
       </c>
       <c r="E23" t="n">
-        <v>16.0866</v>
+        <v>16.2012</v>
       </c>
       <c r="F23" t="n">
-        <v>21.0678</v>
+        <v>20.8686</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>16.1344</v>
+        <v>16.8813</v>
       </c>
       <c r="C24" t="n">
-        <v>21.6398</v>
+        <v>21.8194</v>
       </c>
       <c r="D24" t="n">
-        <v>26.8834</v>
+        <v>26.8062</v>
       </c>
       <c r="E24" t="n">
-        <v>15.825</v>
+        <v>16.1866</v>
       </c>
       <c r="F24" t="n">
-        <v>20.9484</v>
+        <v>20.9351</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>16.1443</v>
+        <v>16.8892</v>
       </c>
       <c r="C25" t="n">
-        <v>21.5597</v>
+        <v>21.2801</v>
       </c>
       <c r="D25" t="n">
-        <v>27.319</v>
+        <v>26.7564</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1957</v>
+        <v>16.2053</v>
       </c>
       <c r="F25" t="n">
-        <v>20.9851</v>
+        <v>22.0856</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.9273</v>
+        <v>16.8888</v>
       </c>
       <c r="C26" t="n">
-        <v>21.5892</v>
+        <v>21.5259</v>
       </c>
       <c r="D26" t="n">
-        <v>27.5792</v>
+        <v>27.8499</v>
       </c>
       <c r="E26" t="n">
-        <v>16.2594</v>
+        <v>16.2444</v>
       </c>
       <c r="F26" t="n">
-        <v>21.7892</v>
+        <v>22.2552</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.9158</v>
+        <v>16.9212</v>
       </c>
       <c r="C27" t="n">
-        <v>21.903</v>
+        <v>21.2205</v>
       </c>
       <c r="D27" t="n">
-        <v>28.3114</v>
+        <v>28.3379</v>
       </c>
       <c r="E27" t="n">
-        <v>16.6371</v>
+        <v>16.4027</v>
       </c>
       <c r="F27" t="n">
-        <v>21.3887</v>
+        <v>21.4882</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>17.019</v>
+        <v>16.9845</v>
       </c>
       <c r="C28" t="n">
-        <v>21.9392</v>
+        <v>21.9996</v>
       </c>
       <c r="D28" t="n">
-        <v>28.7278</v>
+        <v>28.8516</v>
       </c>
       <c r="E28" t="n">
-        <v>16.7772</v>
+        <v>16.5111</v>
       </c>
       <c r="F28" t="n">
-        <v>21.8564</v>
+        <v>21.4137</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>16.2148</v>
+        <v>16.9836</v>
       </c>
       <c r="C29" t="n">
-        <v>21.6824</v>
+        <v>22.1068</v>
       </c>
       <c r="D29" t="n">
-        <v>29.0497</v>
+        <v>29.4452</v>
       </c>
       <c r="E29" t="n">
-        <v>16.5672</v>
+        <v>17.2535</v>
       </c>
       <c r="F29" t="n">
-        <v>21.4507</v>
+        <v>22.4274</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>16.9983</v>
+        <v>16.9621</v>
       </c>
       <c r="C30" t="n">
-        <v>21.4997</v>
+        <v>21.9372</v>
       </c>
       <c r="D30" t="n">
-        <v>29.5999</v>
+        <v>29.8002</v>
       </c>
       <c r="E30" t="n">
-        <v>16.6645</v>
+        <v>16.8405</v>
       </c>
       <c r="F30" t="n">
-        <v>21.3873</v>
+        <v>21.1102</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>16.9365</v>
+        <v>17.0245</v>
       </c>
       <c r="C31" t="n">
-        <v>21.3288</v>
+        <v>21.5034</v>
       </c>
       <c r="D31" t="n">
-        <v>30.1176</v>
+        <v>30.4965</v>
       </c>
       <c r="E31" t="n">
-        <v>16.4546</v>
+        <v>16.7448</v>
       </c>
       <c r="F31" t="n">
-        <v>21.7841</v>
+        <v>21.3239</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>17.0936</v>
+        <v>17.0904</v>
       </c>
       <c r="C32" t="n">
-        <v>21.8102</v>
+        <v>21.1896</v>
       </c>
       <c r="D32" t="n">
-        <v>30.9687</v>
+        <v>30.6659</v>
       </c>
       <c r="E32" t="n">
-        <v>17.6842</v>
+        <v>16.795</v>
       </c>
       <c r="F32" t="n">
-        <v>22.1728</v>
+        <v>21.2245</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>17.1069</v>
+        <v>17.1343</v>
       </c>
       <c r="C33" t="n">
-        <v>21.9175</v>
+        <v>21.7037</v>
       </c>
       <c r="D33" t="n">
-        <v>31.5484</v>
+        <v>31.5286</v>
       </c>
       <c r="E33" t="n">
-        <v>17.0682</v>
+        <v>17.0521</v>
       </c>
       <c r="F33" t="n">
-        <v>22.7309</v>
+        <v>22.3983</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>17.1961</v>
+        <v>17.1934</v>
       </c>
       <c r="C34" t="n">
-        <v>22.5181</v>
+        <v>22.1691</v>
       </c>
       <c r="D34" t="n">
-        <v>32.1231</v>
+        <v>31.7402</v>
       </c>
       <c r="E34" t="n">
-        <v>17.574</v>
+        <v>17.633</v>
       </c>
       <c r="F34" t="n">
-        <v>22.2182</v>
+        <v>23.3962</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.2866</v>
+        <v>17.2482</v>
       </c>
       <c r="C35" t="n">
-        <v>22.792</v>
+        <v>22.3146</v>
       </c>
       <c r="D35" t="n">
-        <v>26.9526</v>
+        <v>26.807</v>
       </c>
       <c r="E35" t="n">
-        <v>18.6312</v>
+        <v>18.7144</v>
       </c>
       <c r="F35" t="n">
-        <v>22.6353</v>
+        <v>24.0247</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.4743</v>
+        <v>17.4311</v>
       </c>
       <c r="C36" t="n">
-        <v>22.7477</v>
+        <v>22.6823</v>
       </c>
       <c r="D36" t="n">
-        <v>27.0017</v>
+        <v>27.3025</v>
       </c>
       <c r="E36" t="n">
-        <v>18.7164</v>
+        <v>18.6488</v>
       </c>
       <c r="F36" t="n">
-        <v>23.7128</v>
+        <v>23.6781</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>17.7017</v>
+        <v>17.7169</v>
       </c>
       <c r="C37" t="n">
-        <v>22.9158</v>
+        <v>22.9581</v>
       </c>
       <c r="D37" t="n">
-        <v>27.3297</v>
+        <v>27.7032</v>
       </c>
       <c r="E37" t="n">
-        <v>17.286</v>
+        <v>17.7081</v>
       </c>
       <c r="F37" t="n">
-        <v>24.1392</v>
+        <v>23.9107</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>18.2469</v>
+        <v>18.2259</v>
       </c>
       <c r="C38" t="n">
-        <v>24.0206</v>
+        <v>24.2786</v>
       </c>
       <c r="D38" t="n">
-        <v>28.3995</v>
+        <v>27.9388</v>
       </c>
       <c r="E38" t="n">
-        <v>17.7578</v>
+        <v>17.8418</v>
       </c>
       <c r="F38" t="n">
-        <v>23.6928</v>
+        <v>24.6374</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.7434</v>
+        <v>18.3516</v>
       </c>
       <c r="C39" t="n">
-        <v>23.8772</v>
+        <v>23.9986</v>
       </c>
       <c r="D39" t="n">
-        <v>28.9624</v>
+        <v>29.5894</v>
       </c>
       <c r="E39" t="n">
-        <v>17.4352</v>
+        <v>17.7363</v>
       </c>
       <c r="F39" t="n">
-        <v>23.7407</v>
+        <v>23.7617</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>18.8004</v>
+        <v>18.7717</v>
       </c>
       <c r="C40" t="n">
-        <v>24.422</v>
+        <v>24.3197</v>
       </c>
       <c r="D40" t="n">
-        <v>29.1492</v>
+        <v>29.3021</v>
       </c>
       <c r="E40" t="n">
-        <v>18.0388</v>
+        <v>18.3282</v>
       </c>
       <c r="F40" t="n">
-        <v>23.927</v>
+        <v>24.7294</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>18.6783</v>
+        <v>18.7097</v>
       </c>
       <c r="C41" t="n">
-        <v>24.4677</v>
+        <v>24.3498</v>
       </c>
       <c r="D41" t="n">
-        <v>29.6739</v>
+        <v>29.5325</v>
       </c>
       <c r="E41" t="n">
-        <v>17.9381</v>
+        <v>18.4938</v>
       </c>
       <c r="F41" t="n">
-        <v>23.4739</v>
+        <v>23.8277</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>17.7082</v>
+        <v>18.7556</v>
       </c>
       <c r="C42" t="n">
-        <v>24.054</v>
+        <v>24.0933</v>
       </c>
       <c r="D42" t="n">
-        <v>30.1068</v>
+        <v>30.5072</v>
       </c>
       <c r="E42" t="n">
-        <v>18.1563</v>
+        <v>18.3836</v>
       </c>
       <c r="F42" t="n">
-        <v>24.6463</v>
+        <v>23.2684</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>18.4093</v>
+        <v>18.3216</v>
       </c>
       <c r="C43" t="n">
-        <v>24.2582</v>
+        <v>24.1264</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8175</v>
+        <v>31.7384</v>
       </c>
       <c r="E43" t="n">
-        <v>18.505</v>
+        <v>18.0145</v>
       </c>
       <c r="F43" t="n">
-        <v>23.9333</v>
+        <v>24.6069</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>18.7409</v>
+        <v>18.7984</v>
       </c>
       <c r="C44" t="n">
-        <v>24.295</v>
+        <v>24.544</v>
       </c>
       <c r="D44" t="n">
-        <v>31.3409</v>
+        <v>31.4441</v>
       </c>
       <c r="E44" t="n">
-        <v>18.8825</v>
+        <v>18.6956</v>
       </c>
       <c r="F44" t="n">
-        <v>23.8157</v>
+        <v>24.0265</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>18.4943</v>
+        <v>18.6625</v>
       </c>
       <c r="C45" t="n">
-        <v>24.4261</v>
+        <v>24.2884</v>
       </c>
       <c r="D45" t="n">
-        <v>32.2858</v>
+        <v>32.1161</v>
       </c>
       <c r="E45" t="n">
-        <v>18.6571</v>
+        <v>18.6925</v>
       </c>
       <c r="F45" t="n">
-        <v>23.9433</v>
+        <v>24.3462</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>18.4928</v>
+        <v>18.7121</v>
       </c>
       <c r="C46" t="n">
-        <v>24.3438</v>
+        <v>24.7216</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9142</v>
+        <v>32.6866</v>
       </c>
       <c r="E46" t="n">
-        <v>18.7251</v>
+        <v>18.7745</v>
       </c>
       <c r="F46" t="n">
-        <v>24.6843</v>
+        <v>23.7207</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>18.5033</v>
+        <v>18.795</v>
       </c>
       <c r="C47" t="n">
-        <v>24.1443</v>
+        <v>24.4014</v>
       </c>
       <c r="D47" t="n">
-        <v>33.3618</v>
+        <v>33.6195</v>
       </c>
       <c r="E47" t="n">
-        <v>18.9783</v>
+        <v>18.7023</v>
       </c>
       <c r="F47" t="n">
-        <v>24.5275</v>
+        <v>24.4258</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>19.4271</v>
+        <v>18.8083</v>
       </c>
       <c r="C48" t="n">
-        <v>24.7899</v>
+        <v>24.8196</v>
       </c>
       <c r="D48" t="n">
-        <v>34.5155</v>
+        <v>34.803</v>
       </c>
       <c r="E48" t="n">
-        <v>19.3521</v>
+        <v>19.3219</v>
       </c>
       <c r="F48" t="n">
-        <v>25.5278</v>
+        <v>24.7956</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>19.0347</v>
+        <v>18.9954</v>
       </c>
       <c r="C49" t="n">
-        <v>24.6959</v>
+        <v>24.8475</v>
       </c>
       <c r="D49" t="n">
-        <v>35.6923</v>
+        <v>35.5625</v>
       </c>
       <c r="E49" t="n">
-        <v>19.9305</v>
+        <v>19.9224</v>
       </c>
       <c r="F49" t="n">
-        <v>26.0097</v>
+        <v>25.2024</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>18.1652</v>
+        <v>18.9098</v>
       </c>
       <c r="C50" t="n">
-        <v>24.786</v>
+        <v>24.8132</v>
       </c>
       <c r="D50" t="n">
-        <v>30.0932</v>
+        <v>30.0626</v>
       </c>
       <c r="E50" t="n">
-        <v>20.4904</v>
+        <v>20.4648</v>
       </c>
       <c r="F50" t="n">
-        <v>25.2395</v>
+        <v>26.5311</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>19.2728</v>
+        <v>19.4177</v>
       </c>
       <c r="C51" t="n">
-        <v>24.3396</v>
+        <v>25.5316</v>
       </c>
       <c r="D51" t="n">
-        <v>32.1872</v>
+        <v>31.2144</v>
       </c>
       <c r="E51" t="n">
-        <v>19.09</v>
+        <v>19.0875</v>
       </c>
       <c r="F51" t="n">
-        <v>25.2704</v>
+        <v>25.4532</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>19.9932</v>
+        <v>19.9922</v>
       </c>
       <c r="C52" t="n">
-        <v>26.0182</v>
+        <v>25.998</v>
       </c>
       <c r="D52" t="n">
-        <v>32.4551</v>
+        <v>32.6839</v>
       </c>
       <c r="E52" t="n">
-        <v>19.1897</v>
+        <v>19.1281</v>
       </c>
       <c r="F52" t="n">
-        <v>25.2972</v>
+        <v>26.0001</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>20.8765</v>
+        <v>20.8383</v>
       </c>
       <c r="C53" t="n">
-        <v>25.9138</v>
+        <v>26.0257</v>
       </c>
       <c r="D53" t="n">
-        <v>35.0284</v>
+        <v>33.5906</v>
       </c>
       <c r="E53" t="n">
-        <v>18.8209</v>
+        <v>18.8432</v>
       </c>
       <c r="F53" t="n">
-        <v>25.3311</v>
+        <v>25.7358</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>21.1089</v>
+        <v>21.0297</v>
       </c>
       <c r="C54" t="n">
-        <v>26.3705</v>
+        <v>26.1061</v>
       </c>
       <c r="D54" t="n">
-        <v>34.6783</v>
+        <v>35.6162</v>
       </c>
       <c r="E54" t="n">
-        <v>19.3945</v>
+        <v>19.5292</v>
       </c>
       <c r="F54" t="n">
-        <v>25.3407</v>
+        <v>25.3983</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>20.9173</v>
+        <v>20.1765</v>
       </c>
       <c r="C55" t="n">
-        <v>25.9912</v>
+        <v>26.0691</v>
       </c>
       <c r="D55" t="n">
-        <v>40.1837</v>
+        <v>34.8058</v>
       </c>
       <c r="E55" t="n">
-        <v>19.0256</v>
+        <v>19.4573</v>
       </c>
       <c r="F55" t="n">
-        <v>25.7799</v>
+        <v>25.4709</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>20.1825</v>
+        <v>20.8053</v>
       </c>
       <c r="C56" t="n">
-        <v>26.2117</v>
+        <v>26.3251</v>
       </c>
       <c r="D56" t="n">
-        <v>38.1972</v>
+        <v>37.9504</v>
       </c>
       <c r="E56" t="n">
-        <v>19.7641</v>
+        <v>19.574</v>
       </c>
       <c r="F56" t="n">
-        <v>25.6847</v>
+        <v>25.6437</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>20.5099</v>
+        <v>21.0467</v>
       </c>
       <c r="C57" t="n">
-        <v>26.0139</v>
+        <v>26.0843</v>
       </c>
       <c r="D57" t="n">
-        <v>36.9767</v>
+        <v>39.6806</v>
       </c>
       <c r="E57" t="n">
-        <v>19.8753</v>
+        <v>19.7596</v>
       </c>
       <c r="F57" t="n">
-        <v>25.6002</v>
+        <v>25.5697</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9154</v>
+        <v>20.9214</v>
       </c>
       <c r="C58" t="n">
-        <v>26.4327</v>
+        <v>26.2597</v>
       </c>
       <c r="D58" t="n">
-        <v>41.5426</v>
+        <v>41.7872</v>
       </c>
       <c r="E58" t="n">
-        <v>19.8987</v>
+        <v>19.9227</v>
       </c>
       <c r="F58" t="n">
-        <v>25.9609</v>
+        <v>25.7827</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.9978</v>
+        <v>21.0438</v>
       </c>
       <c r="C59" t="n">
-        <v>26.0663</v>
+        <v>26.2044</v>
       </c>
       <c r="D59" t="n">
-        <v>44.4199</v>
+        <v>44.8415</v>
       </c>
       <c r="E59" t="n">
-        <v>20.0611</v>
+        <v>20.0421</v>
       </c>
       <c r="F59" t="n">
-        <v>25.707</v>
+        <v>25.3359</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.3603</v>
+        <v>20.2631</v>
       </c>
       <c r="C60" t="n">
-        <v>26.5125</v>
+        <v>26.351</v>
       </c>
       <c r="D60" t="n">
-        <v>47.4476</v>
+        <v>47.7436</v>
       </c>
       <c r="E60" t="n">
-        <v>20.2677</v>
+        <v>20.3077</v>
       </c>
       <c r="F60" t="n">
-        <v>26.2943</v>
+        <v>26.052</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>21.1555</v>
+        <v>21.0889</v>
       </c>
       <c r="C61" t="n">
-        <v>26.1392</v>
+        <v>25.8687</v>
       </c>
       <c r="D61" t="n">
-        <v>48.754</v>
+        <v>50.6356</v>
       </c>
       <c r="E61" t="n">
-        <v>20.3461</v>
+        <v>20.5357</v>
       </c>
       <c r="F61" t="n">
-        <v>25.7588</v>
+        <v>26.2278</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>21.0925</v>
+        <v>20.3691</v>
       </c>
       <c r="C62" t="n">
-        <v>26.4722</v>
+        <v>26.53</v>
       </c>
       <c r="D62" t="n">
-        <v>54.714</v>
+        <v>54.1461</v>
       </c>
       <c r="E62" t="n">
-        <v>20.8572</v>
+        <v>20.9561</v>
       </c>
       <c r="F62" t="n">
-        <v>26.0076</v>
+        <v>27.2644</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>21.2013</v>
+        <v>20.6926</v>
       </c>
       <c r="C63" t="n">
-        <v>26.4649</v>
+        <v>26.5204</v>
       </c>
       <c r="D63" t="n">
-        <v>54.2994</v>
+        <v>58.1009</v>
       </c>
       <c r="E63" t="n">
-        <v>21.3304</v>
+        <v>21.3139</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9114</v>
+        <v>27.2267</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>21.2587</v>
+        <v>21.3486</v>
       </c>
       <c r="C64" t="n">
-        <v>26.8807</v>
+        <v>27.0372</v>
       </c>
       <c r="D64" t="n">
-        <v>58.6508</v>
+        <v>59.2698</v>
       </c>
       <c r="E64" t="n">
-        <v>21.9689</v>
+        <v>22.0163</v>
       </c>
       <c r="F64" t="n">
-        <v>27.3983</v>
+        <v>27.7097</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>21.6698</v>
+        <v>21.1154</v>
       </c>
       <c r="C65" t="n">
-        <v>27.0566</v>
+        <v>26.6337</v>
       </c>
       <c r="D65" t="n">
-        <v>61.4104</v>
+        <v>62.4503</v>
       </c>
       <c r="E65" t="n">
-        <v>22.2927</v>
+        <v>22.8033</v>
       </c>
       <c r="F65" t="n">
-        <v>28.4567</v>
+        <v>29.1698</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.2485</v>
+        <v>22.0505</v>
       </c>
       <c r="C66" t="n">
-        <v>27.9883</v>
+        <v>27.9557</v>
       </c>
       <c r="D66" t="n">
-        <v>64.5089</v>
+        <v>66.2231</v>
       </c>
       <c r="E66" t="n">
-        <v>19.6264</v>
+        <v>19.6777</v>
       </c>
       <c r="F66" t="n">
-        <v>28.2938</v>
+        <v>27.8981</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>21.9351</v>
+        <v>23.1722</v>
       </c>
       <c r="C67" t="n">
-        <v>32.355</v>
+        <v>29.65</v>
       </c>
       <c r="D67" t="n">
-        <v>67.89830000000001</v>
+        <v>69.4226</v>
       </c>
       <c r="E67" t="n">
-        <v>19.9461</v>
+        <v>20.3545</v>
       </c>
       <c r="F67" t="n">
-        <v>27.7483</v>
+        <v>27.9321</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>21.9599</v>
+        <v>23.2801</v>
       </c>
       <c r="C68" t="n">
-        <v>31.2684</v>
+        <v>30.7056</v>
       </c>
       <c r="D68" t="n">
-        <v>71.06180000000001</v>
+        <v>73.1186</v>
       </c>
       <c r="E68" t="n">
-        <v>19.8477</v>
+        <v>20.5628</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5588</v>
+        <v>29.5559</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>23.1957</v>
+        <v>23.3569</v>
       </c>
       <c r="C69" t="n">
-        <v>31.4685</v>
+        <v>32.9619</v>
       </c>
       <c r="D69" t="n">
-        <v>77.7133</v>
+        <v>79.2788</v>
       </c>
       <c r="E69" t="n">
-        <v>20.2669</v>
+        <v>20.5271</v>
       </c>
       <c r="F69" t="n">
-        <v>29.7182</v>
+        <v>29.0929</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>23.6186</v>
+        <v>24.4493</v>
       </c>
       <c r="C70" t="n">
-        <v>32.1435</v>
+        <v>31.9076</v>
       </c>
       <c r="D70" t="n">
-        <v>76.6669</v>
+        <v>79.08629999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>19.9552</v>
+        <v>20.1847</v>
       </c>
       <c r="F70" t="n">
-        <v>29.7144</v>
+        <v>30.0312</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>23.4037</v>
+        <v>23.5771</v>
       </c>
       <c r="C71" t="n">
-        <v>30.7551</v>
+        <v>32.6393</v>
       </c>
       <c r="D71" t="n">
-        <v>80.9359</v>
+        <v>81.5288</v>
       </c>
       <c r="E71" t="n">
-        <v>20.0491</v>
+        <v>20.7293</v>
       </c>
       <c r="F71" t="n">
-        <v>34.1743</v>
+        <v>29.3399</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>23.7689</v>
+        <v>23.4805</v>
       </c>
       <c r="C72" t="n">
-        <v>33.6829</v>
+        <v>33.6452</v>
       </c>
       <c r="D72" t="n">
-        <v>85.2102</v>
+        <v>85.53919999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>19.7153</v>
+        <v>20.9692</v>
       </c>
       <c r="F72" t="n">
-        <v>28.7992</v>
+        <v>29.6007</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>23.3694</v>
+        <v>23.1855</v>
       </c>
       <c r="C73" t="n">
-        <v>32.4466</v>
+        <v>32.6683</v>
       </c>
       <c r="D73" t="n">
-        <v>88.2179</v>
+        <v>90.3557</v>
       </c>
       <c r="E73" t="n">
-        <v>20.3325</v>
+        <v>21.05</v>
       </c>
       <c r="F73" t="n">
-        <v>29.2025</v>
+        <v>29.0837</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>23.2417</v>
+        <v>23.2995</v>
       </c>
       <c r="C74" t="n">
-        <v>32.7573</v>
+        <v>32.8261</v>
       </c>
       <c r="D74" t="n">
-        <v>92.2088</v>
+        <v>94.5986</v>
       </c>
       <c r="E74" t="n">
-        <v>20.4387</v>
+        <v>20.816</v>
       </c>
       <c r="F74" t="n">
-        <v>28.0311</v>
+        <v>29.7635</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>23.2726</v>
+        <v>22.088</v>
       </c>
       <c r="C75" t="n">
-        <v>32.7857</v>
+        <v>33.3603</v>
       </c>
       <c r="D75" t="n">
-        <v>96.40689999999999</v>
+        <v>98.3113</v>
       </c>
       <c r="E75" t="n">
-        <v>20.6694</v>
+        <v>21.7403</v>
       </c>
       <c r="F75" t="n">
-        <v>29.3338</v>
+        <v>30.3264</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>23.3593</v>
+        <v>22.173</v>
       </c>
       <c r="C76" t="n">
-        <v>32.8775</v>
+        <v>34.0496</v>
       </c>
       <c r="D76" t="n">
-        <v>100.442</v>
+        <v>102.687</v>
       </c>
       <c r="E76" t="n">
-        <v>21.1592</v>
+        <v>21.9832</v>
       </c>
       <c r="F76" t="n">
-        <v>31.4941</v>
+        <v>32.6378</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>23.4469</v>
+        <v>24.0142</v>
       </c>
       <c r="C77" t="n">
-        <v>33.2108</v>
+        <v>32.2688</v>
       </c>
       <c r="D77" t="n">
-        <v>104.626</v>
+        <v>106.852</v>
       </c>
       <c r="E77" t="n">
-        <v>21.013</v>
+        <v>22.7977</v>
       </c>
       <c r="F77" t="n">
-        <v>30.1186</v>
+        <v>30.8775</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>23.6095</v>
+        <v>23.6565</v>
       </c>
       <c r="C78" t="n">
-        <v>34.2015</v>
+        <v>34.3339</v>
       </c>
       <c r="D78" t="n">
-        <v>99.0818</v>
+        <v>101.734</v>
       </c>
       <c r="E78" t="n">
-        <v>21.5701</v>
+        <v>22.8137</v>
       </c>
       <c r="F78" t="n">
-        <v>31.1671</v>
+        <v>34.5585</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>24.0026</v>
+        <v>24.6712</v>
       </c>
       <c r="C79" t="n">
-        <v>33.3097</v>
+        <v>34.8546</v>
       </c>
       <c r="D79" t="n">
-        <v>99.9068</v>
+        <v>103.701</v>
       </c>
       <c r="E79" t="n">
-        <v>22.8572</v>
+        <v>23.6048</v>
       </c>
       <c r="F79" t="n">
-        <v>32.8196</v>
+        <v>35.326</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>24.6985</v>
+        <v>24.9464</v>
       </c>
       <c r="C80" t="n">
-        <v>35.7959</v>
+        <v>35.607</v>
       </c>
       <c r="D80" t="n">
-        <v>103.469</v>
+        <v>107.596</v>
       </c>
       <c r="E80" t="n">
-        <v>27.059</v>
+        <v>28.4651</v>
       </c>
       <c r="F80" t="n">
-        <v>57.5039</v>
+        <v>60.0167</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>45.0016</v>
+        <v>40.4374</v>
       </c>
       <c r="C81" t="n">
-        <v>65.20910000000001</v>
+        <v>67.0831</v>
       </c>
       <c r="D81" t="n">
-        <v>107.058</v>
+        <v>110.622</v>
       </c>
       <c r="E81" t="n">
-        <v>28.2574</v>
+        <v>27.4679</v>
       </c>
       <c r="F81" t="n">
-        <v>60.6027</v>
+        <v>57.8262</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>44.2102</v>
+        <v>45.3712</v>
       </c>
       <c r="C82" t="n">
-        <v>66.28440000000001</v>
+        <v>67.9935</v>
       </c>
       <c r="D82" t="n">
-        <v>107.746</v>
+        <v>110.988</v>
       </c>
       <c r="E82" t="n">
-        <v>30.4666</v>
+        <v>28.0283</v>
       </c>
       <c r="F82" t="n">
-        <v>58.7642</v>
+        <v>59.9857</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>38.5318</v>
+        <v>41.7676</v>
       </c>
       <c r="C83" t="n">
-        <v>63.4704</v>
+        <v>68.07340000000001</v>
       </c>
       <c r="D83" t="n">
-        <v>111.737</v>
+        <v>116.086</v>
       </c>
       <c r="E83" t="n">
-        <v>27.8373</v>
+        <v>28.3527</v>
       </c>
       <c r="F83" t="n">
-        <v>59.3812</v>
+        <v>61.7004</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.7841</v>
+        <v>45.0909</v>
       </c>
       <c r="C84" t="n">
-        <v>65.49720000000001</v>
+        <v>65.9569</v>
       </c>
       <c r="D84" t="n">
-        <v>112.87</v>
+        <v>118.505</v>
       </c>
       <c r="E84" t="n">
-        <v>29.7487</v>
+        <v>29.1447</v>
       </c>
       <c r="F84" t="n">
-        <v>59.7156</v>
+        <v>61.4121</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>44.1697</v>
+        <v>45.5786</v>
       </c>
       <c r="C85" t="n">
-        <v>64.152</v>
+        <v>67.6677</v>
       </c>
       <c r="D85" t="n">
-        <v>116.566</v>
+        <v>121.501</v>
       </c>
       <c r="E85" t="n">
-        <v>30.3962</v>
+        <v>29.0899</v>
       </c>
       <c r="F85" t="n">
-        <v>58.1798</v>
+        <v>60.7064</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>40.2435</v>
+        <v>45.1433</v>
       </c>
       <c r="C86" t="n">
-        <v>64.5043</v>
+        <v>67.74160000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>119.901</v>
+        <v>125.141</v>
       </c>
       <c r="E86" t="n">
-        <v>29.7328</v>
+        <v>27.3141</v>
       </c>
       <c r="F86" t="n">
-        <v>59.6763</v>
+        <v>61.0377</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>44.5354</v>
+        <v>45.264</v>
       </c>
       <c r="C87" t="n">
-        <v>64.1932</v>
+        <v>65.496</v>
       </c>
       <c r="D87" t="n">
-        <v>136.731</v>
+        <v>138.917</v>
       </c>
       <c r="E87" t="n">
-        <v>30.461</v>
+        <v>31.6719</v>
       </c>
       <c r="F87" t="n">
-        <v>60.8267</v>
+        <v>58.9491</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>46.8278</v>
+        <v>43.8915</v>
       </c>
       <c r="C88" t="n">
-        <v>64.0454</v>
+        <v>66.5398</v>
       </c>
       <c r="D88" t="n">
-        <v>128.254</v>
+        <v>132.38</v>
       </c>
       <c r="E88" t="n">
-        <v>32.5633</v>
+        <v>35.9146</v>
       </c>
       <c r="F88" t="n">
-        <v>58.4714</v>
+        <v>58.556</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>44.5403</v>
+        <v>45.5344</v>
       </c>
       <c r="C89" t="n">
-        <v>63.9768</v>
+        <v>68.193</v>
       </c>
       <c r="D89" t="n">
-        <v>134.93</v>
+        <v>137.737</v>
       </c>
       <c r="E89" t="n">
-        <v>31.7359</v>
+        <v>32.7445</v>
       </c>
       <c r="F89" t="n">
-        <v>61.1912</v>
+        <v>58.6071</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.3935</v>
+        <v>46.1295</v>
       </c>
       <c r="C90" t="n">
-        <v>66.29770000000001</v>
+        <v>68.71559999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>134.953</v>
+        <v>138.777</v>
       </c>
       <c r="E90" t="n">
-        <v>28.1647</v>
+        <v>32.7963</v>
       </c>
       <c r="F90" t="n">
-        <v>59.3979</v>
+        <v>61.6535</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>43.0715</v>
+        <v>44.7213</v>
       </c>
       <c r="C91" t="n">
-        <v>64.47490000000001</v>
+        <v>65.74850000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>140.746</v>
+        <v>145.137</v>
       </c>
       <c r="E91" t="n">
-        <v>33.0106</v>
+        <v>34.3407</v>
       </c>
       <c r="F91" t="n">
-        <v>60.9128</v>
+        <v>62.2893</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>44.5833</v>
+        <v>42.4105</v>
       </c>
       <c r="C92" t="n">
-        <v>65.91419999999999</v>
+        <v>66.65470000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>123.819</v>
+        <v>127.792</v>
       </c>
       <c r="E92" t="n">
-        <v>33.9565</v>
+        <v>35.1052</v>
       </c>
       <c r="F92" t="n">
-        <v>61.5944</v>
+        <v>61.4018</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>45.1165</v>
+        <v>45.8137</v>
       </c>
       <c r="C93" t="n">
-        <v>64.092</v>
+        <v>68.0014</v>
       </c>
       <c r="D93" t="n">
-        <v>125.78</v>
+        <v>129.967</v>
       </c>
       <c r="E93" t="n">
-        <v>30.982</v>
+        <v>35.7133</v>
       </c>
       <c r="F93" t="n">
-        <v>62.4255</v>
+        <v>59.8174</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.6542</v>
+        <v>45.694</v>
       </c>
       <c r="C94" t="n">
-        <v>67.15860000000001</v>
+        <v>69.31910000000001</v>
       </c>
       <c r="D94" t="n">
-        <v>126.972</v>
+        <v>132.456</v>
       </c>
       <c r="E94" t="n">
-        <v>52.3676</v>
+        <v>52.2192</v>
       </c>
       <c r="F94" t="n">
-        <v>85.2319</v>
+        <v>87.7092</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>72.9457</v>
+        <v>75.0128</v>
       </c>
       <c r="C95" t="n">
-        <v>91.43389999999999</v>
+        <v>90.6114</v>
       </c>
       <c r="D95" t="n">
-        <v>131.419</v>
+        <v>134.948</v>
       </c>
       <c r="E95" t="n">
-        <v>57.0656</v>
+        <v>56.5034</v>
       </c>
       <c r="F95" t="n">
-        <v>84.95350000000001</v>
+        <v>86.837</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>72.9517</v>
+        <v>73.3138</v>
       </c>
       <c r="C96" t="n">
-        <v>89.8785</v>
+        <v>92.60599999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>133.125</v>
+        <v>137.007</v>
       </c>
       <c r="E96" t="n">
-        <v>57.77</v>
+        <v>57.5963</v>
       </c>
       <c r="F96" t="n">
-        <v>85.8085</v>
+        <v>86.7358</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>72.6803</v>
+        <v>71.0612</v>
       </c>
       <c r="C97" t="n">
-        <v>90.2281</v>
+        <v>93.3394</v>
       </c>
       <c r="D97" t="n">
-        <v>135.831</v>
+        <v>140.335</v>
       </c>
       <c r="E97" t="n">
-        <v>57.7606</v>
+        <v>57.3215</v>
       </c>
       <c r="F97" t="n">
-        <v>84.5629</v>
+        <v>87.2941</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>72.2885</v>
+        <v>74.4473</v>
       </c>
       <c r="C98" t="n">
-        <v>89.459</v>
+        <v>93.3558</v>
       </c>
       <c r="D98" t="n">
-        <v>138.726</v>
+        <v>140.629</v>
       </c>
       <c r="E98" t="n">
-        <v>58.0845</v>
+        <v>57.5121</v>
       </c>
       <c r="F98" t="n">
-        <v>92.3189</v>
+        <v>93.58759999999999</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>72.81480000000001</v>
+        <v>74.52079999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>89.5108</v>
+        <v>92.2251</v>
       </c>
       <c r="D99" t="n">
-        <v>142.382</v>
+        <v>146.815</v>
       </c>
       <c r="E99" t="n">
-        <v>58.8629</v>
+        <v>58.6004</v>
       </c>
       <c r="F99" t="n">
-        <v>85.3656</v>
+        <v>86.66379999999999</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>72.8402</v>
+        <v>74.745</v>
       </c>
       <c r="C100" t="n">
-        <v>90.7757</v>
+        <v>93.602</v>
       </c>
       <c r="D100" t="n">
-        <v>145.341</v>
+        <v>150.038</v>
       </c>
       <c r="E100" t="n">
-        <v>59.7491</v>
+        <v>59.2134</v>
       </c>
       <c r="F100" t="n">
-        <v>93.0377</v>
+        <v>93.136</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.66419999999999</v>
+        <v>74.2115</v>
       </c>
       <c r="C101" t="n">
-        <v>89.611</v>
+        <v>93.8347</v>
       </c>
       <c r="D101" t="n">
-        <v>148.267</v>
+        <v>153.72</v>
       </c>
       <c r="E101" t="n">
-        <v>58.7738</v>
+        <v>59.5781</v>
       </c>
       <c r="F101" t="n">
-        <v>87.3293</v>
+        <v>89.11620000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>71.5622</v>
+        <v>74.398</v>
       </c>
       <c r="C102" t="n">
-        <v>89.08929999999999</v>
+        <v>93.29900000000001</v>
       </c>
       <c r="D102" t="n">
-        <v>154.802</v>
+        <v>156.87</v>
       </c>
       <c r="E102" t="n">
-        <v>60.9188</v>
+        <v>60.0283</v>
       </c>
       <c r="F102" t="n">
-        <v>86.70869999999999</v>
+        <v>87.7034</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>67.4486</v>
+        <v>74.4881</v>
       </c>
       <c r="C103" t="n">
-        <v>90.6973</v>
+        <v>93.3425</v>
       </c>
       <c r="D103" t="n">
-        <v>156.963</v>
+        <v>161.244</v>
       </c>
       <c r="E103" t="n">
-        <v>61.4233</v>
+        <v>60.6371</v>
       </c>
       <c r="F103" t="n">
-        <v>87.3446</v>
+        <v>88.2715</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>72.45099999999999</v>
+        <v>74.5513</v>
       </c>
       <c r="C104" t="n">
-        <v>89.0185</v>
+        <v>93.8824</v>
       </c>
       <c r="D104" t="n">
-        <v>178.619</v>
+        <v>181.165</v>
       </c>
       <c r="E104" t="n">
-        <v>61.7118</v>
+        <v>61.4075</v>
       </c>
       <c r="F104" t="n">
-        <v>86.68470000000001</v>
+        <v>90.1254</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>71.2122</v>
+        <v>72.054</v>
       </c>
       <c r="C105" t="n">
-        <v>90.6469</v>
+        <v>99.7291</v>
       </c>
       <c r="D105" t="n">
-        <v>180.298</v>
+        <v>184.497</v>
       </c>
       <c r="E105" t="n">
-        <v>62.3603</v>
+        <v>61.6479</v>
       </c>
       <c r="F105" t="n">
-        <v>89.9132</v>
+        <v>91.5467</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>71.8167</v>
+        <v>74.25790000000001</v>
       </c>
       <c r="C106" t="n">
-        <v>91.9058</v>
+        <v>100.044</v>
       </c>
       <c r="D106" t="n">
-        <v>183.255</v>
+        <v>185.15</v>
       </c>
       <c r="E106" t="n">
-        <v>62.9726</v>
+        <v>62.5541</v>
       </c>
       <c r="F106" t="n">
-        <v>88.7255</v>
+        <v>92.1485</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>72.3237</v>
+        <v>74.1345</v>
       </c>
       <c r="C107" t="n">
-        <v>92.5226</v>
+        <v>93.9931</v>
       </c>
       <c r="D107" t="n">
-        <v>139.575</v>
+        <v>143.78</v>
       </c>
       <c r="E107" t="n">
-        <v>60.1689</v>
+        <v>63.4419</v>
       </c>
       <c r="F107" t="n">
-        <v>90.4033</v>
+        <v>91.4139</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>69.41379999999999</v>
+        <v>74.2791</v>
       </c>
       <c r="C108" t="n">
-        <v>93.8477</v>
+        <v>95.6799</v>
       </c>
       <c r="D108" t="n">
-        <v>142.242</v>
+        <v>144.293</v>
       </c>
       <c r="E108" t="n">
-        <v>77.1683</v>
+        <v>78.24890000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>107.272</v>
+        <v>109.333</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>71.7704</v>
+        <v>74.1044</v>
       </c>
       <c r="C109" t="n">
-        <v>93.2146</v>
+        <v>95.2517</v>
       </c>
       <c r="D109" t="n">
-        <v>143.034</v>
+        <v>147.795</v>
       </c>
       <c r="E109" t="n">
-        <v>77.4833</v>
+        <v>78.08929999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>108.64</v>
+        <v>112.029</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>86.7865</v>
+        <v>91.5213</v>
       </c>
       <c r="C110" t="n">
-        <v>110.6</v>
+        <v>116.477</v>
       </c>
       <c r="D110" t="n">
-        <v>146.336</v>
+        <v>150.243</v>
       </c>
       <c r="E110" t="n">
-        <v>78.6498</v>
+        <v>78.7597</v>
       </c>
       <c r="F110" t="n">
-        <v>109.984</v>
+        <v>113.048</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>88.22580000000001</v>
+        <v>91.10899999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>112.782</v>
+        <v>115.977</v>
       </c>
       <c r="D111" t="n">
-        <v>148.935</v>
+        <v>153.51</v>
       </c>
       <c r="E111" t="n">
-        <v>76.79989999999999</v>
+        <v>77.6567</v>
       </c>
       <c r="F111" t="n">
-        <v>110.091</v>
+        <v>110.45</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.27549999999999</v>
+        <v>90.7633</v>
       </c>
       <c r="C112" t="n">
-        <v>112.625</v>
+        <v>113.115</v>
       </c>
       <c r="D112" t="n">
-        <v>150.924</v>
+        <v>156.439</v>
       </c>
       <c r="E112" t="n">
-        <v>79.15219999999999</v>
+        <v>79.9115</v>
       </c>
       <c r="F112" t="n">
-        <v>109.902</v>
+        <v>110.789</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>88.584</v>
+        <v>90.3413</v>
       </c>
       <c r="C113" t="n">
-        <v>113.541</v>
+        <v>115.511</v>
       </c>
       <c r="D113" t="n">
-        <v>155.654</v>
+        <v>159.685</v>
       </c>
       <c r="E113" t="n">
-        <v>79.3441</v>
+        <v>93.628</v>
       </c>
       <c r="F113" t="n">
-        <v>111.477</v>
+        <v>111.236</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>87.4297</v>
+        <v>88.47929999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>111.169</v>
+        <v>113.291</v>
       </c>
       <c r="D114" t="n">
-        <v>158.377</v>
+        <v>159.013</v>
       </c>
       <c r="E114" t="n">
-        <v>79.95229999999999</v>
+        <v>78.6656</v>
       </c>
       <c r="F114" t="n">
-        <v>110.915</v>
+        <v>112.903</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>88.2064</v>
+        <v>87.9962</v>
       </c>
       <c r="C115" t="n">
-        <v>112.355</v>
+        <v>114.102</v>
       </c>
       <c r="D115" t="n">
-        <v>161.807</v>
+        <v>166.725</v>
       </c>
       <c r="E115" t="n">
-        <v>79.05889999999999</v>
+        <v>81.8648</v>
       </c>
       <c r="F115" t="n">
-        <v>112.076</v>
+        <v>113.43</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>86.96550000000001</v>
+        <v>90.9961</v>
       </c>
       <c r="C116" t="n">
-        <v>113.463</v>
+        <v>117.783</v>
       </c>
       <c r="D116" t="n">
-        <v>165.974</v>
+        <v>170.294</v>
       </c>
       <c r="E116" t="n">
-        <v>81.0951</v>
+        <v>81.6447</v>
       </c>
       <c r="F116" t="n">
-        <v>111.088</v>
+        <v>114.319</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>88.2204</v>
+        <v>90.6108</v>
       </c>
       <c r="C117" t="n">
-        <v>114.986</v>
+        <v>118.192</v>
       </c>
       <c r="D117" t="n">
-        <v>170.535</v>
+        <v>175.751</v>
       </c>
       <c r="E117" t="n">
-        <v>79.98650000000001</v>
+        <v>82.271</v>
       </c>
       <c r="F117" t="n">
-        <v>114.375</v>
+        <v>116.887</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>89.2576</v>
+        <v>110.086</v>
       </c>
       <c r="C118" t="n">
-        <v>111.644</v>
+        <v>115.385</v>
       </c>
       <c r="D118" t="n">
-        <v>180.536</v>
+        <v>186.262</v>
       </c>
       <c r="E118" t="n">
-        <v>82.6388</v>
+        <v>83.211</v>
       </c>
       <c r="F118" t="n">
-        <v>112.061</v>
+        <v>116.471</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>88.52030000000001</v>
+        <v>110.755</v>
       </c>
       <c r="C119" t="n">
-        <v>113.596</v>
+        <v>135.378</v>
       </c>
       <c r="D119" t="n">
-        <v>178.914</v>
+        <v>185.465</v>
       </c>
       <c r="E119" t="n">
-        <v>83.1528</v>
+        <v>85.3205</v>
       </c>
       <c r="F119" t="n">
-        <v>115.174</v>
+        <v>117.557</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>88.1712</v>
+        <v>92.11669999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>114.307</v>
+        <v>118.353</v>
       </c>
       <c r="D120" t="n">
-        <v>195.461</v>
+        <v>200.04</v>
       </c>
       <c r="E120" t="n">
-        <v>83.82250000000001</v>
+        <v>85.0333</v>
       </c>
       <c r="F120" t="n">
-        <v>113.588</v>
+        <v>116.645</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>89.30840000000001</v>
+        <v>88.0021</v>
       </c>
       <c r="C121" t="n">
-        <v>114.187</v>
+        <v>118.192</v>
       </c>
       <c r="D121" t="n">
-        <v>145.728</v>
+        <v>150.407</v>
       </c>
       <c r="E121" t="n">
-        <v>85.964</v>
+        <v>86.4063</v>
       </c>
       <c r="F121" t="n">
-        <v>117.724</v>
+        <v>119.814</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>90.2076</v>
+        <v>91.5402</v>
       </c>
       <c r="C122" t="n">
-        <v>112.168</v>
+        <v>119.01</v>
       </c>
       <c r="D122" t="n">
-        <v>148.693</v>
+        <v>153.534</v>
       </c>
       <c r="E122" t="n">
-        <v>86.48099999999999</v>
+        <v>85.0102</v>
       </c>
       <c r="F122" t="n">
-        <v>119.221</v>
+        <v>121.126</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>102.939</v>
+        <v>91.4119</v>
       </c>
       <c r="C123" t="n">
-        <v>114.724</v>
+        <v>115.581</v>
       </c>
       <c r="D123" t="n">
-        <v>151.443</v>
+        <v>156.026</v>
       </c>
       <c r="E123" t="n">
-        <v>92.6429</v>
+        <v>95.84010000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>133.421</v>
+        <v>137.352</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>112.815</v>
+        <v>114.998</v>
       </c>
       <c r="C124" t="n">
-        <v>134.441</v>
+        <v>138.559</v>
       </c>
       <c r="D124" t="n">
-        <v>153.504</v>
+        <v>158.157</v>
       </c>
       <c r="E124" t="n">
-        <v>92.9992</v>
+        <v>96.0382</v>
       </c>
       <c r="F124" t="n">
-        <v>132.888</v>
+        <v>135.603</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>110.934</v>
+        <v>114.357</v>
       </c>
       <c r="C125" t="n">
-        <v>137.126</v>
+        <v>141.29</v>
       </c>
       <c r="D125" t="n">
-        <v>156.234</v>
+        <v>161.198</v>
       </c>
       <c r="E125" t="n">
-        <v>93.3648</v>
+        <v>96.7046</v>
       </c>
       <c r="F125" t="n">
-        <v>133.656</v>
+        <v>138.05</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>112.148</v>
+        <v>115.356</v>
       </c>
       <c r="C126" t="n">
-        <v>137.292</v>
+        <v>139.407</v>
       </c>
       <c r="D126" t="n">
-        <v>158.944</v>
+        <v>163.879</v>
       </c>
       <c r="E126" t="n">
-        <v>93.5427</v>
+        <v>97.3819</v>
       </c>
       <c r="F126" t="n">
-        <v>134.036</v>
+        <v>139.042</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>109.144</v>
+        <v>113.882</v>
       </c>
       <c r="C127" t="n">
-        <v>136.729</v>
+        <v>141.647</v>
       </c>
       <c r="D127" t="n">
-        <v>161.715</v>
+        <v>167.323</v>
       </c>
       <c r="E127" t="n">
-        <v>92.7508</v>
+        <v>98.5864</v>
       </c>
       <c r="F127" t="n">
-        <v>132.689</v>
+        <v>133.28</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>111.181</v>
+        <v>110.236</v>
       </c>
       <c r="C128" t="n">
-        <v>137.494</v>
+        <v>138.474</v>
       </c>
       <c r="D128" t="n">
-        <v>165.622</v>
+        <v>166.583</v>
       </c>
       <c r="E128" t="n">
-        <v>94.95569999999999</v>
+        <v>93.8459</v>
       </c>
       <c r="F128" t="n">
-        <v>133.271</v>
+        <v>136.054</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>108.457</v>
+        <v>112.248</v>
       </c>
       <c r="C129" t="n">
-        <v>137.418</v>
+        <v>138.446</v>
       </c>
       <c r="D129" t="n">
-        <v>176.896</v>
+        <v>177.718</v>
       </c>
       <c r="E129" t="n">
-        <v>95.7569</v>
+        <v>96.09739999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>135.285</v>
+        <v>134.772</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>112.027</v>
+        <v>112.425</v>
       </c>
       <c r="C130" t="n">
-        <v>142.441</v>
+        <v>137.714</v>
       </c>
       <c r="D130" t="n">
-        <v>183.493</v>
+        <v>179.662</v>
       </c>
       <c r="E130" t="n">
-        <v>99.9935</v>
+        <v>95.13200000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>139.773</v>
+        <v>134.483</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>115.436</v>
+        <v>112.706</v>
       </c>
       <c r="C131" t="n">
-        <v>136.431</v>
+        <v>139.054</v>
       </c>
       <c r="D131" t="n">
-        <v>183.281</v>
+        <v>184.214</v>
       </c>
       <c r="E131" t="n">
-        <v>96.89449999999999</v>
+        <v>97.25230000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>136.053</v>
+        <v>136.453</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>115.147</v>
+        <v>113.578</v>
       </c>
       <c r="C132" t="n">
-        <v>136.211</v>
+        <v>142.153</v>
       </c>
       <c r="D132" t="n">
-        <v>186.76</v>
+        <v>191.315</v>
       </c>
       <c r="E132" t="n">
-        <v>97.301</v>
+        <v>122.174</v>
       </c>
       <c r="F132" t="n">
-        <v>136.918</v>
+        <v>136.862</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>110.881</v>
+        <v>112.279</v>
       </c>
       <c r="C133" t="n">
-        <v>139.257</v>
+        <v>139.414</v>
       </c>
       <c r="D133" t="n">
-        <v>191.686</v>
+        <v>192.464</v>
       </c>
       <c r="E133" t="n">
-        <v>97.3524</v>
+        <v>99.24339999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>137.857</v>
+        <v>138.221</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>113.402</v>
+        <v>112.493</v>
       </c>
       <c r="C134" t="n">
-        <v>149.884</v>
+        <v>138.92</v>
       </c>
       <c r="D134" t="n">
-        <v>194.718</v>
+        <v>195.474</v>
       </c>
       <c r="E134" t="n">
-        <v>98.8318</v>
+        <v>100.038</v>
       </c>
       <c r="F134" t="n">
-        <v>142.884</v>
+        <v>140.265</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>119.137</v>
+        <v>112.452</v>
       </c>
       <c r="C135" t="n">
-        <v>143.335</v>
+        <v>139.829</v>
       </c>
       <c r="D135" t="n">
-        <v>156.311</v>
+        <v>151.978</v>
       </c>
       <c r="E135" t="n">
-        <v>105.473</v>
+        <v>101.719</v>
       </c>
       <c r="F135" t="n">
-        <v>142.631</v>
+        <v>141.247</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>116.299</v>
+        <v>112.824</v>
       </c>
       <c r="C136" t="n">
-        <v>144.884</v>
+        <v>140.74</v>
       </c>
       <c r="D136" t="n">
-        <v>159.44</v>
+        <v>154.851</v>
       </c>
       <c r="E136" t="n">
-        <v>108.387</v>
+        <v>101.848</v>
       </c>
       <c r="F136" t="n">
-        <v>145.106</v>
+        <v>142.603</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>116.812</v>
+        <v>113.835</v>
       </c>
       <c r="C137" t="n">
-        <v>146.531</v>
+        <v>144.855</v>
       </c>
       <c r="D137" t="n">
-        <v>164.087</v>
+        <v>160.068</v>
       </c>
       <c r="E137" t="n">
-        <v>108.302</v>
+        <v>101.123</v>
       </c>
       <c r="F137" t="n">
-        <v>154.436</v>
+        <v>149.463</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>139.303</v>
+        <v>135.476</v>
       </c>
       <c r="C138" t="n">
-        <v>158.772</v>
+        <v>152.432</v>
       </c>
       <c r="D138" t="n">
-        <v>166.484</v>
+        <v>162.045</v>
       </c>
       <c r="E138" t="n">
-        <v>109.773</v>
+        <v>102.585</v>
       </c>
       <c r="F138" t="n">
-        <v>153.163</v>
+        <v>148.764</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>139.691</v>
+        <v>135.522</v>
       </c>
       <c r="C139" t="n">
-        <v>159.048</v>
+        <v>154.163</v>
       </c>
       <c r="D139" t="n">
-        <v>169.2</v>
+        <v>164.685</v>
       </c>
       <c r="E139" t="n">
-        <v>110.345</v>
+        <v>101.774</v>
       </c>
       <c r="F139" t="n">
-        <v>154.69</v>
+        <v>149.247</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>139.65</v>
+        <v>135.388</v>
       </c>
       <c r="C140" t="n">
-        <v>159.461</v>
+        <v>154.354</v>
       </c>
       <c r="D140" t="n">
-        <v>171.337</v>
+        <v>167.351</v>
       </c>
       <c r="E140" t="n">
-        <v>110.397</v>
+        <v>103.458</v>
       </c>
       <c r="F140" t="n">
-        <v>154.153</v>
+        <v>148.733</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>139.069</v>
+        <v>135.218</v>
       </c>
       <c r="C141" t="n">
-        <v>158.768</v>
+        <v>154.078</v>
       </c>
       <c r="D141" t="n">
-        <v>174.479</v>
+        <v>170.416</v>
       </c>
       <c r="E141" t="n">
-        <v>110.217</v>
+        <v>103.762</v>
       </c>
       <c r="F141" t="n">
-        <v>148.722</v>
+        <v>150.08</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>134.795</v>
+        <v>135.636</v>
       </c>
       <c r="C142" t="n">
-        <v>153.595</v>
+        <v>154.208</v>
       </c>
       <c r="D142" t="n">
-        <v>173.074</v>
+        <v>173.65</v>
       </c>
       <c r="E142" t="n">
-        <v>102.316</v>
+        <v>104.259</v>
       </c>
       <c r="F142" t="n">
-        <v>149.594</v>
+        <v>150.057</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>134.238</v>
+        <v>134.875</v>
       </c>
       <c r="C143" t="n">
-        <v>153.853</v>
+        <v>154.826</v>
       </c>
       <c r="D143" t="n">
-        <v>175.72</v>
+        <v>176.506</v>
       </c>
       <c r="E143" t="n">
-        <v>104.159</v>
+        <v>104.695</v>
       </c>
       <c r="F143" t="n">
-        <v>149.717</v>
+        <v>150.358</v>
       </c>
     </row>
   </sheetData>
